--- a/Dashboards/Data final/variacion_pobreza_significancia.xlsx
+++ b/Dashboards/Data final/variacion_pobreza_significancia.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N205"/>
+  <dimension ref="A1:N251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11034,6 +11034,2398 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206">
+        <v>2009</v>
+      </c>
+      <c r="B206">
+        <v>2008</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F206">
+        <v>45.37225662596507</v>
+      </c>
+      <c r="G206">
+        <v>0.2267407234365869</v>
+      </c>
+      <c r="H206">
+        <v>46.40958476072698</v>
+      </c>
+      <c r="I206">
+        <v>0.2286926477158213</v>
+      </c>
+      <c r="J206">
+        <v>-1.037328134761907</v>
+      </c>
+      <c r="K206">
+        <v>-2.235159267444516</v>
+      </c>
+      <c r="L206">
+        <v>-3.221085973298846</v>
+      </c>
+      <c r="M206">
+        <v>0.001277058325049651</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>2010</v>
+      </c>
+      <c r="B207">
+        <v>2009</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F207">
+        <v>41.70233143895541</v>
+      </c>
+      <c r="G207">
+        <v>0.220419492077931</v>
+      </c>
+      <c r="H207">
+        <v>45.37225662596507</v>
+      </c>
+      <c r="I207">
+        <v>0.2267407234365869</v>
+      </c>
+      <c r="J207">
+        <v>-3.66992518700966</v>
+      </c>
+      <c r="K207">
+        <v>-8.088478422537797</v>
+      </c>
+      <c r="L207">
+        <v>-11.60554827069085</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>2011</v>
+      </c>
+      <c r="B208">
+        <v>2010</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F208">
+        <v>38.82951242869445</v>
+      </c>
+      <c r="G208">
+        <v>0.2731599736958909</v>
+      </c>
+      <c r="H208">
+        <v>41.70233143895541</v>
+      </c>
+      <c r="I208">
+        <v>0.220419492077931</v>
+      </c>
+      <c r="J208">
+        <v>-2.872819010260962</v>
+      </c>
+      <c r="K208">
+        <v>-6.888869065908805</v>
+      </c>
+      <c r="L208">
+        <v>-8.184665435417134</v>
+      </c>
+      <c r="M208">
+        <v>2.220446049250313E-16</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>2012</v>
+      </c>
+      <c r="B209">
+        <v>2011</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F209">
+        <v>36.10111701381651</v>
+      </c>
+      <c r="G209">
+        <v>0.2362000216701784</v>
+      </c>
+      <c r="H209">
+        <v>38.82951242869445</v>
+      </c>
+      <c r="I209">
+        <v>0.2731599736958909</v>
+      </c>
+      <c r="J209">
+        <v>-2.728395414877944</v>
+      </c>
+      <c r="K209">
+        <v>-7.026602303823159</v>
+      </c>
+      <c r="L209">
+        <v>-7.555394683920438</v>
+      </c>
+      <c r="M209">
+        <v>4.174438572590589E-14</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>2013</v>
+      </c>
+      <c r="B210">
+        <v>2012</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F210">
+        <v>38.0788339905707</v>
+      </c>
+      <c r="G210">
+        <v>0.2216410490512503</v>
+      </c>
+      <c r="H210">
+        <v>36.10111701381651</v>
+      </c>
+      <c r="I210">
+        <v>0.2362000216701784</v>
+      </c>
+      <c r="J210">
+        <v>1.977716976754195</v>
+      </c>
+      <c r="K210">
+        <v>5.478270869007431</v>
+      </c>
+      <c r="L210">
+        <v>6.10583304594434</v>
+      </c>
+      <c r="M210">
+        <v>1.022658624449946E-09</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>2014</v>
+      </c>
+      <c r="B211">
+        <v>2013</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F211">
+        <v>34.98412862171275</v>
+      </c>
+      <c r="G211">
+        <v>0.2212022891840079</v>
+      </c>
+      <c r="H211">
+        <v>38.0788339905707</v>
+      </c>
+      <c r="I211">
+        <v>0.2216410490512503</v>
+      </c>
+      <c r="J211">
+        <v>-3.094705368857952</v>
+      </c>
+      <c r="K211">
+        <v>-8.127101185987682</v>
+      </c>
+      <c r="L211">
+        <v>-9.882890354664424</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>2015</v>
+      </c>
+      <c r="B212">
+        <v>2014</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F212">
+        <v>32.6624181266378</v>
+      </c>
+      <c r="G212">
+        <v>0.204910367336961</v>
+      </c>
+      <c r="H212">
+        <v>34.98412862171275</v>
+      </c>
+      <c r="I212">
+        <v>0.2212022891840079</v>
+      </c>
+      <c r="J212">
+        <v>-2.321710495074953</v>
+      </c>
+      <c r="K212">
+        <v>-6.636467982895517</v>
+      </c>
+      <c r="L212">
+        <v>-7.699835176448132</v>
+      </c>
+      <c r="M212">
+        <v>1.354472090042691E-14</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>2016</v>
+      </c>
+      <c r="B213">
+        <v>2015</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F213">
+        <v>31.42578065969976</v>
+      </c>
+      <c r="G213">
+        <v>0.2159027922846497</v>
+      </c>
+      <c r="H213">
+        <v>32.6624181266378</v>
+      </c>
+      <c r="I213">
+        <v>0.204910367336961</v>
+      </c>
+      <c r="J213">
+        <v>-1.236637466938031</v>
+      </c>
+      <c r="K213">
+        <v>-3.786117311165927</v>
+      </c>
+      <c r="L213">
+        <v>-4.154511498755168</v>
+      </c>
+      <c r="M213">
+        <v>3.25983224891413E-05</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>2017</v>
+      </c>
+      <c r="B214">
+        <v>2016</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F214">
+        <v>31.61905495073139</v>
+      </c>
+      <c r="G214">
+        <v>0.2200538103971073</v>
+      </c>
+      <c r="H214">
+        <v>31.42578065969976</v>
+      </c>
+      <c r="I214">
+        <v>0.2159027922846497</v>
+      </c>
+      <c r="J214">
+        <v>0.1932742910316207</v>
+      </c>
+      <c r="K214">
+        <v>0.6150182651770193</v>
+      </c>
+      <c r="L214">
+        <v>0.6269402332615115</v>
+      </c>
+      <c r="M214">
+        <v>0.5306984130332921</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>2018</v>
+      </c>
+      <c r="B215">
+        <v>2017</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F215">
+        <v>33.92937108926956</v>
+      </c>
+      <c r="G215">
+        <v>0.9803490548465044</v>
+      </c>
+      <c r="H215">
+        <v>31.61905495073139</v>
+      </c>
+      <c r="I215">
+        <v>0.2200538103971073</v>
+      </c>
+      <c r="J215">
+        <v>2.310316138538173</v>
+      </c>
+      <c r="K215">
+        <v>7.306721033054572</v>
+      </c>
+      <c r="L215">
+        <v>2.299410659973029</v>
+      </c>
+      <c r="M215">
+        <v>0.02148163119478408</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>2019</v>
+      </c>
+      <c r="B216">
+        <v>2018</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F216">
+        <v>34.48778963331205</v>
+      </c>
+      <c r="G216">
+        <v>1.23313427756701</v>
+      </c>
+      <c r="H216">
+        <v>33.92937108926956</v>
+      </c>
+      <c r="I216">
+        <v>0.9803490548465044</v>
+      </c>
+      <c r="J216">
+        <v>0.5584185440424889</v>
+      </c>
+      <c r="K216">
+        <v>1.645826392046192</v>
+      </c>
+      <c r="L216">
+        <v>0.3544743421769679</v>
+      </c>
+      <c r="M216">
+        <v>0.7229834293209561</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>2020</v>
+      </c>
+      <c r="B217">
+        <v>2019</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F217">
+        <v>33.14917979652057</v>
+      </c>
+      <c r="G217">
+        <v>1.908089794209365</v>
+      </c>
+      <c r="H217">
+        <v>34.48778963331205</v>
+      </c>
+      <c r="I217">
+        <v>1.23313427756701</v>
+      </c>
+      <c r="J217">
+        <v>-1.338609836791477</v>
+      </c>
+      <c r="K217">
+        <v>-3.881402232570168</v>
+      </c>
+      <c r="L217">
+        <v>-0.5892086655869961</v>
+      </c>
+      <c r="M217">
+        <v>0.5557213048009173</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>2021</v>
+      </c>
+      <c r="B218">
+        <v>2020</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F218">
+        <v>33.40554075319305</v>
+      </c>
+      <c r="G218">
+        <v>1.938341103160364</v>
+      </c>
+      <c r="H218">
+        <v>33.14917979652057</v>
+      </c>
+      <c r="I218">
+        <v>1.908089794209365</v>
+      </c>
+      <c r="J218">
+        <v>0.2563609566724807</v>
+      </c>
+      <c r="K218">
+        <v>0.7733553537254911</v>
+      </c>
+      <c r="L218">
+        <v>0.09425307234272849</v>
+      </c>
+      <c r="M218">
+        <v>0.9249081267415851</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>2022</v>
+      </c>
+      <c r="B219">
+        <v>2021</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F219">
+        <v>31.784888112758</v>
+      </c>
+      <c r="G219">
+        <v>2.092442292678036</v>
+      </c>
+      <c r="H219">
+        <v>33.40554075319305</v>
+      </c>
+      <c r="I219">
+        <v>1.938341103160364</v>
+      </c>
+      <c r="J219">
+        <v>-1.620652640435047</v>
+      </c>
+      <c r="K219">
+        <v>-4.851448603717447</v>
+      </c>
+      <c r="L219">
+        <v>-0.5681961989104442</v>
+      </c>
+      <c r="M219">
+        <v>0.5699017521982954</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>2023</v>
+      </c>
+      <c r="B220">
+        <v>2022</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F220">
+        <v>31.09737389148852</v>
+      </c>
+      <c r="G220">
+        <v>2.194337681517109</v>
+      </c>
+      <c r="H220">
+        <v>31.784888112758</v>
+      </c>
+      <c r="I220">
+        <v>2.092442292678036</v>
+      </c>
+      <c r="J220">
+        <v>-0.6875142212694811</v>
+      </c>
+      <c r="K220">
+        <v>-2.16302231057256</v>
+      </c>
+      <c r="L220">
+        <v>-0.226747672350955</v>
+      </c>
+      <c r="M220">
+        <v>0.8206199552489157</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>2024</v>
+      </c>
+      <c r="B221">
+        <v>2023</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>NBI</t>
+        </is>
+      </c>
+      <c r="F221">
+        <v>33.45019864659712</v>
+      </c>
+      <c r="G221">
+        <v>3.444621802289921</v>
+      </c>
+      <c r="H221">
+        <v>31.09737389148852</v>
+      </c>
+      <c r="I221">
+        <v>2.194337681517109</v>
+      </c>
+      <c r="J221">
+        <v>2.352824755108593</v>
+      </c>
+      <c r="K221">
+        <v>7.565991788626788</v>
+      </c>
+      <c r="L221">
+        <v>0.5760823428260282</v>
+      </c>
+      <c r="M221">
+        <v>0.5645595256832445</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>2009</v>
+      </c>
+      <c r="B222">
+        <v>2008</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F222">
+        <v>36.02782335474551</v>
+      </c>
+      <c r="G222">
+        <v>0.2122664731024341</v>
+      </c>
+      <c r="H222">
+        <v>35.09100682507115</v>
+      </c>
+      <c r="I222">
+        <v>0.2105748598981629</v>
+      </c>
+      <c r="J222">
+        <v>0.9368165296743598</v>
+      </c>
+      <c r="K222">
+        <v>2.669676975483761</v>
+      </c>
+      <c r="L222">
+        <v>3.133203725545539</v>
+      </c>
+      <c r="M222">
+        <v>0.001729093824934358</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>2010</v>
+      </c>
+      <c r="B223">
+        <v>2009</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F223">
+        <v>32.76158764874061</v>
+      </c>
+      <c r="G223">
+        <v>0.2047568191384075</v>
+      </c>
+      <c r="H223">
+        <v>36.02782335474551</v>
+      </c>
+      <c r="I223">
+        <v>0.2122664731024341</v>
+      </c>
+      <c r="J223">
+        <v>-3.266235706004906</v>
+      </c>
+      <c r="K223">
+        <v>-9.065870213263061</v>
+      </c>
+      <c r="L223">
+        <v>-11.07469571418391</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>2011</v>
+      </c>
+      <c r="B224">
+        <v>2010</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F224">
+        <v>28.63556567406759</v>
+      </c>
+      <c r="G224">
+        <v>0.2500788898580659</v>
+      </c>
+      <c r="H224">
+        <v>32.76158764874061</v>
+      </c>
+      <c r="I224">
+        <v>0.2047568191384075</v>
+      </c>
+      <c r="J224">
+        <v>-4.126021974673023</v>
+      </c>
+      <c r="K224">
+        <v>-12.59408432494459</v>
+      </c>
+      <c r="L224">
+        <v>-12.76575588509079</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>2012</v>
+      </c>
+      <c r="B225">
+        <v>2011</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F225">
+        <v>27.31012091167221</v>
+      </c>
+      <c r="G225">
+        <v>0.2106039545578149</v>
+      </c>
+      <c r="H225">
+        <v>28.63556567406759</v>
+      </c>
+      <c r="I225">
+        <v>0.2500788898580659</v>
+      </c>
+      <c r="J225">
+        <v>-1.325444762395371</v>
+      </c>
+      <c r="K225">
+        <v>-4.628666244912689</v>
+      </c>
+      <c r="L225">
+        <v>-4.054021351863524</v>
+      </c>
+      <c r="M225">
+        <v>5.034461818520519E-05</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>2013</v>
+      </c>
+      <c r="B226">
+        <v>2012</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F226">
+        <v>25.55254317360288</v>
+      </c>
+      <c r="G226">
+        <v>0.1933176688781958</v>
+      </c>
+      <c r="H226">
+        <v>27.31012091167221</v>
+      </c>
+      <c r="I226">
+        <v>0.2106039545578149</v>
+      </c>
+      <c r="J226">
+        <v>-1.757577738069333</v>
+      </c>
+      <c r="K226">
+        <v>-6.435627816346111</v>
+      </c>
+      <c r="L226">
+        <v>-6.148017488677806</v>
+      </c>
+      <c r="M226">
+        <v>7.845737393097352E-10</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>2015</v>
+      </c>
+      <c r="B227">
+        <v>2013</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F227">
+        <v>23.27724712593939</v>
+      </c>
+      <c r="G227">
+        <v>0.1785403849816009</v>
+      </c>
+      <c r="H227">
+        <v>25.55254317360288</v>
+      </c>
+      <c r="I227">
+        <v>0.1933176688781958</v>
+      </c>
+      <c r="J227">
+        <v>-2.275296047663495</v>
+      </c>
+      <c r="K227">
+        <v>-8.904381971709164</v>
+      </c>
+      <c r="L227">
+        <v>-8.646355175870109</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>2016</v>
+      </c>
+      <c r="B228">
+        <v>2015</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F228">
+        <v>22.91959604796762</v>
+      </c>
+      <c r="G228">
+        <v>0.1890072755199589</v>
+      </c>
+      <c r="H228">
+        <v>23.27724712593939</v>
+      </c>
+      <c r="I228">
+        <v>0.1785403849816009</v>
+      </c>
+      <c r="J228">
+        <v>-0.357651077971763</v>
+      </c>
+      <c r="K228">
+        <v>-1.536483571432331</v>
+      </c>
+      <c r="L228">
+        <v>-1.375576803326172</v>
+      </c>
+      <c r="M228">
+        <v>0.1689526924259517</v>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>2017</v>
+      </c>
+      <c r="B229">
+        <v>2016</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F229">
+        <v>21.46301275720585</v>
+      </c>
+      <c r="G229">
+        <v>0.1863746103076643</v>
+      </c>
+      <c r="H229">
+        <v>22.91959604796762</v>
+      </c>
+      <c r="I229">
+        <v>0.1890072755199589</v>
+      </c>
+      <c r="J229">
+        <v>-1.45658329076177</v>
+      </c>
+      <c r="K229">
+        <v>-6.355187446206896</v>
+      </c>
+      <c r="L229">
+        <v>-5.487396340059181</v>
+      </c>
+      <c r="M229">
+        <v>4.0790123501111E-08</v>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>2018</v>
+      </c>
+      <c r="B230">
+        <v>2017</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F230">
+        <v>23.21899874630216</v>
+      </c>
+      <c r="G230">
+        <v>0.8522631389983094</v>
+      </c>
+      <c r="H230">
+        <v>21.46301275720585</v>
+      </c>
+      <c r="I230">
+        <v>0.1863746103076643</v>
+      </c>
+      <c r="J230">
+        <v>1.75598598909631</v>
+      </c>
+      <c r="K230">
+        <v>8.181451546250264</v>
+      </c>
+      <c r="L230">
+        <v>2.012813897624505</v>
+      </c>
+      <c r="M230">
+        <v>0.04413421130742035</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>2019</v>
+      </c>
+      <c r="B231">
+        <v>2018</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F231">
+        <v>25.03896803269961</v>
+      </c>
+      <c r="G231">
+        <v>1.101374529623826</v>
+      </c>
+      <c r="H231">
+        <v>23.21899874630216</v>
+      </c>
+      <c r="I231">
+        <v>0.8522631389983094</v>
+      </c>
+      <c r="J231">
+        <v>1.819969286397448</v>
+      </c>
+      <c r="K231">
+        <v>7.838276345517676</v>
+      </c>
+      <c r="L231">
+        <v>1.30687121267176</v>
+      </c>
+      <c r="M231">
+        <v>0.1912564544465236</v>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>2020</v>
+      </c>
+      <c r="B232">
+        <v>2019</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F232">
+        <v>32.3631967070786</v>
+      </c>
+      <c r="G232">
+        <v>1.519728417307078</v>
+      </c>
+      <c r="H232">
+        <v>25.03896803269961</v>
+      </c>
+      <c r="I232">
+        <v>1.101374529623826</v>
+      </c>
+      <c r="J232">
+        <v>7.32422867437899</v>
+      </c>
+      <c r="K232">
+        <v>29.25132004168032</v>
+      </c>
+      <c r="L232">
+        <v>3.902385868723504</v>
+      </c>
+      <c r="M232">
+        <v>9.52491537287159E-05</v>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>2021</v>
+      </c>
+      <c r="B233">
+        <v>2020</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F233">
+        <v>27.68524592783522</v>
+      </c>
+      <c r="G233">
+        <v>2.078938057109564</v>
+      </c>
+      <c r="H233">
+        <v>32.3631967070786</v>
+      </c>
+      <c r="I233">
+        <v>1.519728417307078</v>
+      </c>
+      <c r="J233">
+        <v>-4.677950779243382</v>
+      </c>
+      <c r="K233">
+        <v>-14.45453865878522</v>
+      </c>
+      <c r="L233">
+        <v>-1.81655212723515</v>
+      </c>
+      <c r="M233">
+        <v>0.06928571936113603</v>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Marginal (p&lt;0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>2022</v>
+      </c>
+      <c r="B234">
+        <v>2021</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F234">
+        <v>25.22958516444055</v>
+      </c>
+      <c r="G234">
+        <v>1.618086598181598</v>
+      </c>
+      <c r="H234">
+        <v>27.68524592783522</v>
+      </c>
+      <c r="I234">
+        <v>2.078938057109564</v>
+      </c>
+      <c r="J234">
+        <v>-2.455660763394668</v>
+      </c>
+      <c r="K234">
+        <v>-8.869925771277707</v>
+      </c>
+      <c r="L234">
+        <v>-0.9321434741489883</v>
+      </c>
+      <c r="M234">
+        <v>0.351262383247569</v>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>2023</v>
+      </c>
+      <c r="B235">
+        <v>2022</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F235">
+        <v>26.01259632768605</v>
+      </c>
+      <c r="G235">
+        <v>1.958858313258646</v>
+      </c>
+      <c r="H235">
+        <v>25.22958516444055</v>
+      </c>
+      <c r="I235">
+        <v>1.618086598181598</v>
+      </c>
+      <c r="J235">
+        <v>0.7830111632455008</v>
+      </c>
+      <c r="K235">
+        <v>3.103543550724345</v>
+      </c>
+      <c r="L235">
+        <v>0.3081830330791293</v>
+      </c>
+      <c r="M235">
+        <v>0.7579430622194054</v>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>2024</v>
+      </c>
+      <c r="B236">
+        <v>2023</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Pobreza</t>
+        </is>
+      </c>
+      <c r="F236">
+        <v>27.99229671710422</v>
+      </c>
+      <c r="G236">
+        <v>2.962649141244835</v>
+      </c>
+      <c r="H236">
+        <v>26.01259632768605</v>
+      </c>
+      <c r="I236">
+        <v>1.958858313258646</v>
+      </c>
+      <c r="J236">
+        <v>1.979700389418174</v>
+      </c>
+      <c r="K236">
+        <v>7.61054515466076</v>
+      </c>
+      <c r="L236">
+        <v>0.5573986300054464</v>
+      </c>
+      <c r="M236">
+        <v>0.5772551013089462</v>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>2009</v>
+      </c>
+      <c r="B237">
+        <v>2008</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F237">
+        <v>15.40427286412042</v>
+      </c>
+      <c r="G237">
+        <v>0.1457750504585573</v>
+      </c>
+      <c r="H237">
+        <v>15.69408791762872</v>
+      </c>
+      <c r="I237">
+        <v>0.1466792543396998</v>
+      </c>
+      <c r="J237">
+        <v>-0.2898150535083079</v>
+      </c>
+      <c r="K237">
+        <v>-1.846651140412989</v>
+      </c>
+      <c r="L237">
+        <v>-1.401444306321025</v>
+      </c>
+      <c r="M237">
+        <v>0.1610812509414514</v>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>2010</v>
+      </c>
+      <c r="B238">
+        <v>2009</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F238">
+        <v>13.09486215760269</v>
+      </c>
+      <c r="G238">
+        <v>0.1339770104106275</v>
+      </c>
+      <c r="H238">
+        <v>15.40427286412042</v>
+      </c>
+      <c r="I238">
+        <v>0.1457750504585573</v>
+      </c>
+      <c r="J238">
+        <v>-2.309410706517722</v>
+      </c>
+      <c r="K238">
+        <v>-14.99201375416294</v>
+      </c>
+      <c r="L238">
+        <v>-11.66425505978194</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>2011</v>
+      </c>
+      <c r="B239">
+        <v>2010</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F239">
+        <v>11.61226750383311</v>
+      </c>
+      <c r="G239">
+        <v>0.1684338465559491</v>
+      </c>
+      <c r="H239">
+        <v>13.09486215760269</v>
+      </c>
+      <c r="I239">
+        <v>0.1339770104106275</v>
+      </c>
+      <c r="J239">
+        <v>-1.48259465376958</v>
+      </c>
+      <c r="K239">
+        <v>-11.32195693185519</v>
+      </c>
+      <c r="L239">
+        <v>-6.888728871989456</v>
+      </c>
+      <c r="M239">
+        <v>5.629274824059394E-12</v>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>2012</v>
+      </c>
+      <c r="B240">
+        <v>2011</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F240">
+        <v>11.18062047298394</v>
+      </c>
+      <c r="G240">
+        <v>0.1347538599460597</v>
+      </c>
+      <c r="H240">
+        <v>11.61226750383311</v>
+      </c>
+      <c r="I240">
+        <v>0.1684338465559491</v>
+      </c>
+      <c r="J240">
+        <v>-0.4316470308491756</v>
+      </c>
+      <c r="K240">
+        <v>-3.717164031113582</v>
+      </c>
+      <c r="L240">
+        <v>-2.001100663304004</v>
+      </c>
+      <c r="M240">
+        <v>0.04538154288896323</v>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>2013</v>
+      </c>
+      <c r="B241">
+        <v>2012</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F241">
+        <v>8.609753214261628</v>
+      </c>
+      <c r="G241">
+        <v>0.1135674856278471</v>
+      </c>
+      <c r="H241">
+        <v>11.18062047298394</v>
+      </c>
+      <c r="I241">
+        <v>0.1347538599460597</v>
+      </c>
+      <c r="J241">
+        <v>-2.570867258722311</v>
+      </c>
+      <c r="K241">
+        <v>-22.99395874257938</v>
+      </c>
+      <c r="L241">
+        <v>-14.58833271865614</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>2015</v>
+      </c>
+      <c r="B242">
+        <v>2013</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F242">
+        <v>8.45124031311021</v>
+      </c>
+      <c r="G242">
+        <v>0.1077077774605631</v>
+      </c>
+      <c r="H242">
+        <v>8.609753214261628</v>
+      </c>
+      <c r="I242">
+        <v>0.1135674856278471</v>
+      </c>
+      <c r="J242">
+        <v>-0.1585129011514184</v>
+      </c>
+      <c r="K242">
+        <v>-1.841085304150758</v>
+      </c>
+      <c r="L242">
+        <v>-1.01273197193032</v>
+      </c>
+      <c r="M242">
+        <v>0.3111882020676164</v>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>2016</v>
+      </c>
+      <c r="B243">
+        <v>2015</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F243">
+        <v>8.687053233411399</v>
+      </c>
+      <c r="G243">
+        <v>0.118980137454637</v>
+      </c>
+      <c r="H243">
+        <v>8.45124031311021</v>
+      </c>
+      <c r="I243">
+        <v>0.1077077774605631</v>
+      </c>
+      <c r="J243">
+        <v>0.2358129203011892</v>
+      </c>
+      <c r="K243">
+        <v>2.790275883356176</v>
+      </c>
+      <c r="L243">
+        <v>1.46932526888751</v>
+      </c>
+      <c r="M243">
+        <v>0.1417445861846793</v>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>2017</v>
+      </c>
+      <c r="B244">
+        <v>2016</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F244">
+        <v>7.936712514387954</v>
+      </c>
+      <c r="G244">
+        <v>0.1170577360754953</v>
+      </c>
+      <c r="H244">
+        <v>8.687053233411399</v>
+      </c>
+      <c r="I244">
+        <v>0.118980137454637</v>
+      </c>
+      <c r="J244">
+        <v>-0.7503407190234448</v>
+      </c>
+      <c r="K244">
+        <v>-8.637459663969235</v>
+      </c>
+      <c r="L244">
+        <v>-4.495493935587702</v>
+      </c>
+      <c r="M244">
+        <v>6.940863656712537E-06</v>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>2018</v>
+      </c>
+      <c r="B245">
+        <v>2017</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F245">
+        <v>8.413701866138361</v>
+      </c>
+      <c r="G245">
+        <v>0.6776583664138325</v>
+      </c>
+      <c r="H245">
+        <v>7.936712514387954</v>
+      </c>
+      <c r="I245">
+        <v>0.1170577360754953</v>
+      </c>
+      <c r="J245">
+        <v>0.4769893517504062</v>
+      </c>
+      <c r="K245">
+        <v>6.009910915706006</v>
+      </c>
+      <c r="L245">
+        <v>0.6936067226769568</v>
+      </c>
+      <c r="M245">
+        <v>0.4879288766265837</v>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>2019</v>
+      </c>
+      <c r="B246">
+        <v>2018</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F246">
+        <v>8.875431235525305</v>
+      </c>
+      <c r="G246">
+        <v>0.7974166663258746</v>
+      </c>
+      <c r="H246">
+        <v>8.413701866138361</v>
+      </c>
+      <c r="I246">
+        <v>0.6776583664138325</v>
+      </c>
+      <c r="J246">
+        <v>0.4617293693869442</v>
+      </c>
+      <c r="K246">
+        <v>5.487826603949592</v>
+      </c>
+      <c r="L246">
+        <v>0.4412266746286816</v>
+      </c>
+      <c r="M246">
+        <v>0.6590489039187448</v>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>2020</v>
+      </c>
+      <c r="B247">
+        <v>2019</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F247">
+        <v>14.88924546461113</v>
+      </c>
+      <c r="G247">
+        <v>1.539818519660766</v>
+      </c>
+      <c r="H247">
+        <v>8.875431235525305</v>
+      </c>
+      <c r="I247">
+        <v>0.7974166663258746</v>
+      </c>
+      <c r="J247">
+        <v>6.013814229085826</v>
+      </c>
+      <c r="K247">
+        <v>67.75799473285976</v>
+      </c>
+      <c r="L247">
+        <v>3.468082937808147</v>
+      </c>
+      <c r="M247">
+        <v>0.0005241854824244996</v>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Sí (p&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>2021</v>
+      </c>
+      <c r="B248">
+        <v>2020</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F248">
+        <v>10.51103105455558</v>
+      </c>
+      <c r="G248">
+        <v>1.944381543463015</v>
+      </c>
+      <c r="H248">
+        <v>14.88924546461113</v>
+      </c>
+      <c r="I248">
+        <v>1.539818519660766</v>
+      </c>
+      <c r="J248">
+        <v>-4.37821441005555</v>
+      </c>
+      <c r="K248">
+        <v>-29.40521345061926</v>
+      </c>
+      <c r="L248">
+        <v>-1.765228134374159</v>
+      </c>
+      <c r="M248">
+        <v>0.07752543200438566</v>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Marginal (p&lt;0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>2022</v>
+      </c>
+      <c r="B249">
+        <v>2021</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F249">
+        <v>8.247278777916783</v>
+      </c>
+      <c r="G249">
+        <v>1.232037820590771</v>
+      </c>
+      <c r="H249">
+        <v>10.51103105455558</v>
+      </c>
+      <c r="I249">
+        <v>1.944381543463015</v>
+      </c>
+      <c r="J249">
+        <v>-2.263752276638797</v>
+      </c>
+      <c r="K249">
+        <v>-21.53691930781296</v>
+      </c>
+      <c r="L249">
+        <v>-0.9834469176685333</v>
+      </c>
+      <c r="M249">
+        <v>0.3253875285504906</v>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>2023</v>
+      </c>
+      <c r="B250">
+        <v>2022</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F250">
+        <v>9.80936769770728</v>
+      </c>
+      <c r="G250">
+        <v>1.903181209720785</v>
+      </c>
+      <c r="H250">
+        <v>8.247278777916783</v>
+      </c>
+      <c r="I250">
+        <v>1.232037820590771</v>
+      </c>
+      <c r="J250">
+        <v>1.562088919790497</v>
+      </c>
+      <c r="K250">
+        <v>18.94065863243527</v>
+      </c>
+      <c r="L250">
+        <v>0.6890068193473892</v>
+      </c>
+      <c r="M250">
+        <v>0.4908189761803472</v>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>2024</v>
+      </c>
+      <c r="B251">
+        <v>2023</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Pobreza extrema</t>
+        </is>
+      </c>
+      <c r="F251">
+        <v>12.65747844112117</v>
+      </c>
+      <c r="G251">
+        <v>2.623441439666973</v>
+      </c>
+      <c r="H251">
+        <v>9.80936769770728</v>
+      </c>
+      <c r="I251">
+        <v>1.903181209720785</v>
+      </c>
+      <c r="J251">
+        <v>2.848110743413887</v>
+      </c>
+      <c r="K251">
+        <v>29.03460071212917</v>
+      </c>
+      <c r="L251">
+        <v>0.8787559444299686</v>
+      </c>
+      <c r="M251">
+        <v>0.3795336180838669</v>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
